--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N30_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>10.59481005020855</v>
       </c>
       <c r="E2" t="n">
-        <v>3.064707706472094</v>
+        <v>8.581432890321393</v>
       </c>
       <c r="F2" t="n">
-        <v>8.133319336992663</v>
+        <v>8.375128500287161</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,23 +512,55 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
+        <v>8.182634124904814</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7.902703392305953</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8.581432890321393</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8.375128500287161</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>T6165</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W0035F0003T0006Z000C1N30.png</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
         <v>28.66018643102735</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>26.86144872419387</v>
       </c>
-      <c r="E3" t="n">
-        <v>3.064707706472094</v>
-      </c>
-      <c r="F3" t="n">
-        <v>8.133319336992663</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="E4" t="n">
+        <v>8.581432890321393</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8.375128500287161</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>T6165</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.53077101808316</v>
+        <v>3.661250290438514</v>
       </c>
       <c r="D2" t="n">
-        <v>10.59481005020855</v>
+        <v>1.721656633158889</v>
       </c>
       <c r="E2" t="n">
-        <v>8.581432890321393</v>
+        <v>1.394482844677226</v>
       </c>
       <c r="F2" t="n">
-        <v>8.375128500287161</v>
+        <v>1.360958381296664</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.182634124904814</v>
+        <v>1.329678045297032</v>
       </c>
       <c r="D3" t="n">
-        <v>7.902703392305953</v>
+        <v>1.284189301249717</v>
       </c>
       <c r="E3" t="n">
-        <v>8.581432890321393</v>
+        <v>1.394482844677226</v>
       </c>
       <c r="F3" t="n">
-        <v>8.375128500287161</v>
+        <v>1.360958381296664</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.66018643102735</v>
+        <v>4.657280295041945</v>
       </c>
       <c r="D4" t="n">
-        <v>26.86144872419387</v>
+        <v>4.364985417681504</v>
       </c>
       <c r="E4" t="n">
-        <v>8.581432890321393</v>
+        <v>1.394482844677226</v>
       </c>
       <c r="F4" t="n">
-        <v>8.375128500287161</v>
+        <v>1.360958381296664</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
